--- a/docs/downloads/01102026Tduh Developer Project Sales Status 13.xlsx
+++ b/docs/downloads/01102026Tduh Developer Project Sales Status 13.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:BS18"/>
+  <dimension ref="A2:BV18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -562,6 +562,9 @@
     <col width="9" customWidth="1" min="69" max="69"/>
     <col width="9" customWidth="1" min="70" max="70"/>
     <col width="9" customWidth="1" min="71" max="71"/>
+    <col width="9" customWidth="1" min="72" max="72"/>
+    <col width="9" customWidth="1" min="73" max="73"/>
+    <col width="9" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -640,8 +643,11 @@
       <c r="BN3" s="3" t="n">
         <v>46283</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BQ3" s="3" t="n">
         <v>46290</v>
+      </c>
+      <c r="BT3" s="4" t="n">
+        <v>46297</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -988,17 +994,32 @@
           <t>%</t>
         </is>
       </c>
-      <c r="BQ4" s="6" t="inlineStr">
+      <c r="BQ4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW SALES </t>
         </is>
       </c>
-      <c r="BR4" s="6" t="inlineStr">
+      <c r="BR4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="BS4" s="6" t="inlineStr">
+      <c r="BS4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BT4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW SALES </t>
+        </is>
+      </c>
+      <c r="BU4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BV4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1136,15 +1157,26 @@
         <f>BO5/$D$5</f>
         <v/>
       </c>
-      <c r="BQ5" s="12">
+      <c r="BQ5" s="10">
         <f>BR5-BO5</f>
         <v/>
       </c>
-      <c r="BR5" s="12" t="n">
+      <c r="BR5" s="10" t="n">
         <v>229</v>
       </c>
-      <c r="BS5" s="13">
+      <c r="BS5" s="11">
         <f>BR5/$D$5</f>
+        <v/>
+      </c>
+      <c r="BT5" s="12">
+        <f>BU5-BR5</f>
+        <v/>
+      </c>
+      <c r="BU5" s="12" t="n">
+        <v>245</v>
+      </c>
+      <c r="BV5" s="13">
+        <f>BU5/$D$5</f>
         <v/>
       </c>
     </row>
@@ -1400,15 +1432,26 @@
         <f>BO6/$D$6</f>
         <v/>
       </c>
-      <c r="BQ6" s="12">
+      <c r="BQ6" s="10">
         <f>BR6-BO6</f>
         <v/>
       </c>
-      <c r="BR6" s="12" t="n">
+      <c r="BR6" s="10" t="n">
         <v>402</v>
       </c>
-      <c r="BS6" s="13">
+      <c r="BS6" s="11">
         <f>BR6/$D$6</f>
+        <v/>
+      </c>
+      <c r="BT6" s="12">
+        <f>BU6-BR6</f>
+        <v/>
+      </c>
+      <c r="BU6" s="12" t="n">
+        <v>416</v>
+      </c>
+      <c r="BV6" s="13">
+        <f>BU6/$D$6</f>
         <v/>
       </c>
     </row>
@@ -1499,9 +1542,12 @@
       <c r="BN7" s="10" t="n"/>
       <c r="BO7" s="10" t="n"/>
       <c r="BP7" s="11" t="n"/>
-      <c r="BQ7" s="12" t="n"/>
-      <c r="BR7" s="12" t="n"/>
-      <c r="BS7" s="13" t="n"/>
+      <c r="BQ7" s="10" t="n"/>
+      <c r="BR7" s="10" t="n"/>
+      <c r="BS7" s="11" t="n"/>
+      <c r="BT7" s="12" t="n"/>
+      <c r="BU7" s="12" t="n"/>
+      <c r="BV7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1755,15 +1801,26 @@
         <f>BO8/$D$8</f>
         <v/>
       </c>
-      <c r="BQ8" s="12">
+      <c r="BQ8" s="10">
         <f>BR8-BO8</f>
         <v/>
       </c>
-      <c r="BR8" s="12" t="n">
+      <c r="BR8" s="10" t="n">
         <v>1039</v>
       </c>
-      <c r="BS8" s="13">
+      <c r="BS8" s="11">
         <f>BR8/$D$8</f>
+        <v/>
+      </c>
+      <c r="BT8" s="12">
+        <f>BU8-BR8</f>
+        <v/>
+      </c>
+      <c r="BU8" s="12" t="n">
+        <v>1046</v>
+      </c>
+      <c r="BV8" s="13">
+        <f>BU8/$D$8</f>
         <v/>
       </c>
     </row>
@@ -2019,15 +2076,26 @@
         <f>BO9/$D$9</f>
         <v/>
       </c>
-      <c r="BQ9" s="12">
+      <c r="BQ9" s="10">
         <f>BR9-BO9</f>
         <v/>
       </c>
-      <c r="BR9" s="12" t="n">
+      <c r="BR9" s="10" t="n">
         <v>1132</v>
       </c>
-      <c r="BS9" s="13">
+      <c r="BS9" s="11">
         <f>BR9/$D$9</f>
+        <v/>
+      </c>
+      <c r="BT9" s="12">
+        <f>BU9-BR9</f>
+        <v/>
+      </c>
+      <c r="BU9" s="12" t="n">
+        <v>1130</v>
+      </c>
+      <c r="BV9" s="13">
+        <f>BU9/$D$9</f>
         <v/>
       </c>
     </row>
@@ -2283,15 +2351,26 @@
         <f>BO10/$D$10</f>
         <v/>
       </c>
-      <c r="BQ10" s="12">
+      <c r="BQ10" s="10">
         <f>BR10-BO10</f>
         <v/>
       </c>
-      <c r="BR10" s="12" t="n">
+      <c r="BR10" s="10" t="n">
         <v>535</v>
       </c>
-      <c r="BS10" s="13">
+      <c r="BS10" s="11">
         <f>BR10/$D$10</f>
+        <v/>
+      </c>
+      <c r="BT10" s="12">
+        <f>BU10-BR10</f>
+        <v/>
+      </c>
+      <c r="BU10" s="12" t="n">
+        <v>552</v>
+      </c>
+      <c r="BV10" s="13">
+        <f>BU10/$D$10</f>
         <v/>
       </c>
     </row>
@@ -2547,15 +2626,26 @@
         <f>BO11/$D$11</f>
         <v/>
       </c>
-      <c r="BQ11" s="12">
+      <c r="BQ11" s="10">
         <f>BR11-BO11</f>
         <v/>
       </c>
-      <c r="BR11" s="12" t="n">
+      <c r="BR11" s="10" t="n">
         <v>470</v>
       </c>
-      <c r="BS11" s="13">
+      <c r="BS11" s="11">
         <f>BR11/$D$11</f>
+        <v/>
+      </c>
+      <c r="BT11" s="12">
+        <f>BU11-BR11</f>
+        <v/>
+      </c>
+      <c r="BU11" s="12" t="n">
+        <v>470</v>
+      </c>
+      <c r="BV11" s="13">
+        <f>BU11/$D$11</f>
         <v/>
       </c>
     </row>
@@ -2811,15 +2901,26 @@
         <f>BO12/$D$12</f>
         <v/>
       </c>
-      <c r="BQ12" s="12">
+      <c r="BQ12" s="10">
         <f>BR12-BO12</f>
         <v/>
       </c>
-      <c r="BR12" s="12" t="n">
+      <c r="BR12" s="10" t="n">
         <v>239</v>
       </c>
-      <c r="BS12" s="13">
+      <c r="BS12" s="11">
         <f>BR12/$D$12</f>
+        <v/>
+      </c>
+      <c r="BT12" s="12">
+        <f>BU12-BR12</f>
+        <v/>
+      </c>
+      <c r="BU12" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="BV12" s="13">
+        <f>BU12/$D$12</f>
         <v/>
       </c>
     </row>
@@ -3075,15 +3176,26 @@
         <f>BO13/$D$13</f>
         <v/>
       </c>
-      <c r="BQ13" s="12">
+      <c r="BQ13" s="10">
         <f>BR13-BO13</f>
         <v/>
       </c>
-      <c r="BR13" s="12" t="n">
+      <c r="BR13" s="10" t="n">
         <v>684</v>
       </c>
-      <c r="BS13" s="13">
+      <c r="BS13" s="11">
         <f>BR13/$D$13</f>
+        <v/>
+      </c>
+      <c r="BT13" s="12">
+        <f>BU13-BR13</f>
+        <v/>
+      </c>
+      <c r="BU13" s="12" t="n">
+        <v>697</v>
+      </c>
+      <c r="BV13" s="13">
+        <f>BU13/$D$13</f>
         <v/>
       </c>
     </row>
@@ -3339,15 +3451,26 @@
         <f>BO14/$D$14</f>
         <v/>
       </c>
-      <c r="BQ14" s="12">
+      <c r="BQ14" s="10">
         <f>BR14-BO14</f>
         <v/>
       </c>
-      <c r="BR14" s="12" t="n">
+      <c r="BR14" s="10" t="n">
         <v>1179</v>
       </c>
-      <c r="BS14" s="13">
+      <c r="BS14" s="11">
         <f>BR14/$D$14</f>
+        <v/>
+      </c>
+      <c r="BT14" s="12">
+        <f>BU14-BR14</f>
+        <v/>
+      </c>
+      <c r="BU14" s="12" t="n">
+        <v>1186</v>
+      </c>
+      <c r="BV14" s="13">
+        <f>BU14/$D$14</f>
         <v/>
       </c>
     </row>
@@ -3603,15 +3726,26 @@
         <f>BO15/$D$15</f>
         <v/>
       </c>
-      <c r="BQ15" s="12">
+      <c r="BQ15" s="10">
         <f>BR15-BO15</f>
         <v/>
       </c>
-      <c r="BR15" s="12" t="n">
+      <c r="BR15" s="10" t="n">
         <v>153</v>
       </c>
-      <c r="BS15" s="13">
+      <c r="BS15" s="11">
         <f>BR15/$D$15</f>
+        <v/>
+      </c>
+      <c r="BT15" s="12">
+        <f>BU15-BR15</f>
+        <v/>
+      </c>
+      <c r="BU15" s="12" t="n">
+        <v>156</v>
+      </c>
+      <c r="BV15" s="13">
+        <f>BU15/$D$15</f>
         <v/>
       </c>
     </row>
@@ -3803,15 +3937,26 @@
         <f>BO16/$D$16</f>
         <v/>
       </c>
-      <c r="BQ16" s="12">
+      <c r="BQ16" s="10">
         <f>BR16-BO16</f>
         <v/>
       </c>
-      <c r="BR16" s="12" t="n">
+      <c r="BR16" s="10" t="n">
         <v>659</v>
       </c>
-      <c r="BS16" s="13">
+      <c r="BS16" s="11">
         <f>BR16/$D$16</f>
+        <v/>
+      </c>
+      <c r="BT16" s="12">
+        <f>BU16-BR16</f>
+        <v/>
+      </c>
+      <c r="BU16" s="12" t="n">
+        <v>659</v>
+      </c>
+      <c r="BV16" s="13">
+        <f>BU16/$D$16</f>
         <v/>
       </c>
     </row>
@@ -3896,9 +4041,12 @@
       <c r="BN17" s="10" t="n"/>
       <c r="BO17" s="10" t="n"/>
       <c r="BP17" s="11" t="n"/>
-      <c r="BQ17" s="12" t="n"/>
-      <c r="BR17" s="12" t="n"/>
-      <c r="BS17" s="13" t="n"/>
+      <c r="BQ17" s="10" t="n"/>
+      <c r="BR17" s="10" t="n"/>
+      <c r="BS17" s="11" t="n"/>
+      <c r="BT17" s="12" t="n"/>
+      <c r="BU17" s="12" t="n"/>
+      <c r="BV17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -4032,25 +4180,37 @@
         <f>BO18/$D$18</f>
         <v/>
       </c>
-      <c r="BQ18" s="12">
+      <c r="BQ18" s="10">
         <f>BR18-BO18</f>
         <v/>
       </c>
-      <c r="BR18" s="12" t="n">
+      <c r="BR18" s="10" t="n">
         <v>440</v>
       </c>
-      <c r="BS18" s="13">
+      <c r="BS18" s="11">
         <f>BR18/$D$18</f>
+        <v/>
+      </c>
+      <c r="BT18" s="12">
+        <f>BU18-BR18</f>
+        <v/>
+      </c>
+      <c r="BU18" s="12" t="n">
+        <v>465</v>
+      </c>
+      <c r="BV18" s="13">
+        <f>BU18/$D$18</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="U3:W3"/>
+    <mergeCell ref="BT3:BV3"/>
     <mergeCell ref="BK3:BM3"/>
     <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
